--- a/summary/MOZ/MOZ_EWS_export.xlsx
+++ b/summary/MOZ/MOZ_EWS_export.xlsx
@@ -1907,7 +1907,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>weighted</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1959,19 +1959,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>8.16306002048001</v>
+        <v>8.584410483227314</v>
       </c>
       <c r="D2">
-        <v>8.634041587451577</v>
+        <v>8.783794420837125</v>
       </c>
       <c r="E2">
-        <v>8.778361670713677</v>
+        <v>8.856901196880969</v>
       </c>
       <c r="F2">
-        <v>8.708743380908425</v>
+        <v>8.887131936960365</v>
       </c>
       <c r="G2">
-        <v>4.762625258810182</v>
+        <v>6.408028333487984</v>
       </c>
     </row>
     <row r="3">
@@ -1986,19 +1986,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>7.48413211024343</v>
+        <v>7.906745794605714</v>
       </c>
       <c r="D3">
-        <v>8.252898092002575</v>
+        <v>8.349268674807119</v>
       </c>
       <c r="E3">
-        <v>8.053429896526012</v>
+        <v>8.083146885529624</v>
       </c>
       <c r="F3">
-        <v>8.386798657207272</v>
+        <v>8.503883975908046</v>
       </c>
       <c r="G3">
-        <v>3.763828953771249</v>
+        <v>5.845914301255154</v>
       </c>
     </row>
     <row r="4">
@@ -2013,19 +2013,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>6.38173426447091</v>
+        <v>7.071145757830106</v>
       </c>
       <c r="D4">
-        <v>7.411587026700764</v>
+        <v>7.752119098778147</v>
       </c>
       <c r="E4">
-        <v>6.768748404234312</v>
+        <v>7.208858183201993</v>
       </c>
       <c r="F4">
-        <v>7.574899858387348</v>
+        <v>7.939552835114593</v>
       </c>
       <c r="G4">
-        <v>3.587383558010529</v>
+        <v>5.190711578490337</v>
       </c>
     </row>
     <row r="5">
@@ -2040,19 +2040,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>7.868167935260014</v>
+        <v>8.396213101020294</v>
       </c>
       <c r="D5">
-        <v>8.516848662057571</v>
+        <v>8.629912236688487</v>
       </c>
       <c r="E5">
-        <v>8.396089338945909</v>
+        <v>8.683118595850638</v>
       </c>
       <c r="F5">
-        <v>8.492394635930932</v>
+        <v>8.830166314999115</v>
       </c>
       <c r="G5">
-        <v>4.368819171233529</v>
+        <v>5.796749410106194</v>
       </c>
     </row>
     <row r="6">
@@ -2067,19 +2067,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>7.016450997050677</v>
+        <v>7.476711644691411</v>
       </c>
       <c r="D6">
-        <v>7.843945499883571</v>
+        <v>8.057137452178171</v>
       </c>
       <c r="E6">
-        <v>7.459803447948606</v>
+        <v>7.657974264863437</v>
       </c>
       <c r="F6">
-        <v>8.123581625519234</v>
+        <v>8.350870876176653</v>
       </c>
       <c r="G6">
-        <v>3.995284575943186</v>
+        <v>5.409600346662041</v>
       </c>
     </row>
     <row r="7">
@@ -2094,19 +2094,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>7.384750557784504</v>
+        <v>7.514013293051261</v>
       </c>
       <c r="D7">
-        <v>8.219512060919655</v>
+        <v>8.02284630828918</v>
       </c>
       <c r="E7">
-        <v>7.945483882735363</v>
+        <v>7.751497100357531</v>
       </c>
       <c r="F7">
-        <v>8.292147857914898</v>
+        <v>8.255726365723453</v>
       </c>
       <c r="G7">
-        <v>3.454470198408749</v>
+        <v>4.761821299564017</v>
       </c>
     </row>
     <row r="8">
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>6.192224968930876</v>
+        <v>7.327270974334223</v>
       </c>
       <c r="D8">
-        <v>7.097313046702428</v>
+        <v>7.973312505526916</v>
       </c>
       <c r="E8">
-        <v>6.675899212283078</v>
+        <v>7.559059857603591</v>
       </c>
       <c r="F8">
-        <v>7.367413591414604</v>
+        <v>8.220358123999981</v>
       </c>
       <c r="G8">
-        <v>2.951056427743677</v>
+        <v>4.677033800649432</v>
       </c>
     </row>
     <row r="9">
@@ -2148,19 +2148,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>6.668092096721844</v>
+        <v>7.709742010270769</v>
       </c>
       <c r="D9">
-        <v>7.750479980648235</v>
+        <v>8.306997435180149</v>
       </c>
       <c r="E9">
-        <v>7.300176339288301</v>
+        <v>7.860249752213244</v>
       </c>
       <c r="F9">
-        <v>8.057613422227277</v>
+        <v>8.480530914631997</v>
       </c>
       <c r="G9">
-        <v>2.201500990165599</v>
+        <v>4.672972054280907</v>
       </c>
     </row>
     <row r="10">
@@ -2175,19 +2175,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>8.390643434206103</v>
+        <v>8.819080489722884</v>
       </c>
       <c r="D10">
-        <v>8.880444165298877</v>
+        <v>9.054860352914019</v>
       </c>
       <c r="E10">
-        <v>8.925188300613812</v>
+        <v>9.143279642763206</v>
       </c>
       <c r="F10">
-        <v>9.010607626345141</v>
+        <v>9.146285898355849</v>
       </c>
       <c r="G10">
-        <v>5.089795741411343</v>
+        <v>6.127220368349627</v>
       </c>
     </row>
     <row r="11">
@@ -2202,19 +2202,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>6.368180700547843</v>
+        <v>7.157443340558038</v>
       </c>
       <c r="D11">
-        <v>7.290825975706937</v>
+        <v>7.828902082425673</v>
       </c>
       <c r="E11">
-        <v>6.729953361825334</v>
+        <v>7.350225774833183</v>
       </c>
       <c r="F11">
-        <v>7.649934509734569</v>
+        <v>8.089552520225823</v>
       </c>
       <c r="G11">
-        <v>3.369982927967135</v>
+        <v>4.433798771463069</v>
       </c>
     </row>
     <row r="12">
@@ -2229,19 +2229,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>7.966024406031964</v>
+        <v>8.398695269771078</v>
       </c>
       <c r="D12">
-        <v>8.489860949157425</v>
+        <v>8.619481557072902</v>
       </c>
       <c r="E12">
-        <v>8.47995410462989</v>
+        <v>8.716659676152178</v>
       </c>
       <c r="F12">
-        <v>8.657185232304192</v>
+        <v>8.860781719925086</v>
       </c>
       <c r="G12">
-        <v>4.697728009034168</v>
+        <v>5.651727178835374</v>
       </c>
     </row>
     <row r="13">
@@ -2256,19 +2256,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>7.137799689367522</v>
+        <v>7.90003754555317</v>
       </c>
       <c r="D13">
-        <v>7.948736212086145</v>
+        <v>8.451031751539356</v>
       </c>
       <c r="E13">
-        <v>7.663496022080151</v>
+        <v>8.159836984026892</v>
       </c>
       <c r="F13">
-        <v>8.313812552846647</v>
+        <v>8.709403904136101</v>
       </c>
       <c r="G13">
-        <v>3.429373990080568</v>
+        <v>5.018321813889997</v>
       </c>
     </row>
     <row r="14">
@@ -2283,19 +2283,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>8.414018498972904</v>
+        <v>8.857653858259155</v>
       </c>
       <c r="D14">
-        <v>8.996273349397757</v>
+        <v>9.124371506447993</v>
       </c>
       <c r="E14">
-        <v>8.965903697387098</v>
+        <v>9.189292561289021</v>
       </c>
       <c r="F14">
-        <v>8.96070786080181</v>
+        <v>9.149542999113674</v>
       </c>
       <c r="G14">
-        <v>4.812087957159061</v>
+        <v>5.972352723993631</v>
       </c>
     </row>
     <row r="15">
@@ -2310,19 +2310,154 @@
         </is>
       </c>
       <c r="C15">
-        <v>6.146860395635048</v>
+        <v>7.358898480078138</v>
       </c>
       <c r="D15">
-        <v>7.188874691848691</v>
+        <v>8.060134846035206</v>
       </c>
       <c r="E15">
-        <v>6.648780553687696</v>
+        <v>7.65881821854994</v>
       </c>
       <c r="F15">
-        <v>7.396484128803631</v>
+        <v>8.21407319403589</v>
       </c>
       <c r="G15">
-        <v>2.878842117087042</v>
+        <v>4.155791706225973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dissemination</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>8.028792999173319</v>
+      </c>
+      <c r="D16">
+        <v>8.492254218802186</v>
+      </c>
+      <c r="E16">
+        <v>8.296908944261094</v>
+      </c>
+      <c r="F16">
+        <v>8.664310164346345</v>
+      </c>
+      <c r="G16">
+        <v>5.147454945291225</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>7.753787292680046</v>
+      </c>
+      <c r="D17">
+        <v>8.224055813872164</v>
+      </c>
+      <c r="E17">
+        <v>7.971508012041112</v>
+      </c>
+      <c r="F17">
+        <v>8.426812918411743</v>
+      </c>
+      <c r="G17">
+        <v>5.441408438602165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Competency</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>7.952529378440655</v>
+      </c>
+      <c r="D18">
+        <v>8.402894984959927</v>
+      </c>
+      <c r="E18">
+        <v>8.180431387133597</v>
+      </c>
+      <c r="F18">
+        <v>8.556525930754225</v>
+      </c>
+      <c r="G18">
+        <v>5.426602428860591</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>7.809637835908052</v>
+      </c>
+      <c r="D19">
+        <v>8.298501724840174</v>
+      </c>
+      <c r="E19">
+        <v>8.072577932841114</v>
+      </c>
+      <c r="F19">
+        <v>8.53094235554547</v>
+      </c>
+      <c r="G19">
+        <v>5.118204042728169</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EWS INDEX</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>7.891290145926683</v>
+      </c>
+      <c r="D20">
+        <v>8.358155016337175</v>
+      </c>
+      <c r="E20">
+        <v>8.134208478151104</v>
+      </c>
+      <c r="F20">
+        <v>8.545561541379044</v>
+      </c>
+      <c r="G20">
+        <v>5.294431691946695</v>
       </c>
     </row>
   </sheetData>

--- a/summary/MOZ/MOZ_EWS_export.xlsx
+++ b/summary/MOZ/MOZ_EWS_export.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Pillar3" sheetId="1" r:id="rId1"/>
     <sheet name="Pillar4" sheetId="2" r:id="rId2"/>
     <sheet name="Extra_questions" sheetId="3" r:id="rId3"/>
-    <sheet name="Trust Index" sheetId="4" r:id="rId4"/>
-    <sheet name="Sampling_age" sheetId="5" r:id="rId5"/>
-    <sheet name="Sampling_Gender" sheetId="6" r:id="rId6"/>
-    <sheet name="Sampling_Geo" sheetId="7" r:id="rId7"/>
-    <sheet name="Sampling_type" sheetId="8" r:id="rId8"/>
+    <sheet name="Index by profile" sheetId="4" r:id="rId4"/>
+    <sheet name="Index by factors" sheetId="5" r:id="rId5"/>
+    <sheet name="Sampling_age" sheetId="6" r:id="rId6"/>
+    <sheet name="Sampling_Gender" sheetId="7" r:id="rId7"/>
+    <sheet name="Sampling_Geo" sheetId="8" r:id="rId8"/>
+    <sheet name="Sampling_type" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2467,89 +2468,1869 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Age Group</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Total Respondents</t>
+          <t>variable_value</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Percentage (%)</t>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>long_label</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-29</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>485</v>
-      </c>
-      <c r="C2">
-        <v>28.7</v>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>6.137237237237237</v>
+      </c>
+      <c r="E2">
+        <v>438</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>381</v>
-      </c>
-      <c r="C3">
-        <v>22.5</v>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sofala</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>8.120061336310325</v>
+      </c>
+      <c r="E3">
+        <v>1252</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>293</v>
-      </c>
-      <c r="C4">
-        <v>17.3</v>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>6.066628773525325</v>
+      </c>
+      <c r="E4">
+        <v>438</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>222</v>
-      </c>
-      <c r="C5">
-        <v>13.1</v>
+          <t>Provinces</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sofala</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>7.807100546195861</v>
+      </c>
+      <c r="E5">
+        <v>1252</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Provinces</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Buzi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>8.120061336310325</v>
+      </c>
+      <c r="E6">
+        <v>1252</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chigubo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>6.137237237237237</v>
+      </c>
+      <c r="E7">
+        <v>438</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Buzi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>7.807100546195861</v>
+      </c>
+      <c r="E8">
+        <v>1252</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chigubo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>6.066628773525325</v>
+      </c>
+      <c r="E9">
+        <v>438</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Districts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>7.55045074399913</v>
+      </c>
+      <c r="E10">
+        <v>1078</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>7.86747137879542</v>
+      </c>
+      <c r="E11">
+        <v>601</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>7.259736064968623</v>
+      </c>
+      <c r="E12">
+        <v>1078</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>7.656791046843403</v>
+      </c>
+      <c r="E13">
+        <v>601</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>7.714114299427474</v>
+      </c>
+      <c r="E14">
+        <v>485</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30-39</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>8.005592119413258</v>
+      </c>
+      <c r="E15">
+        <v>381</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>7.590888549963283</v>
+      </c>
+      <c r="E16">
+        <v>293</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>7.541383219954648</v>
+      </c>
+      <c r="E17">
+        <v>222</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>60+</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>7.298820701989716</v>
+      </c>
+      <c r="E18">
         <v>309</v>
       </c>
-      <c r="C6">
-        <v>18.3</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18-29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>7.409728622631848</v>
+      </c>
+      <c r="E19">
+        <v>485</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30-39</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>7.708478513356562</v>
+      </c>
+      <c r="E20">
+        <v>381</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>7.327029156816391</v>
+      </c>
+      <c r="E21">
+        <v>293</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>7.436358191075172</v>
+      </c>
+      <c r="E22">
+        <v>222</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>7.037027819257784</v>
+      </c>
+      <c r="E23">
+        <v>309</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Age Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>7.14343149540518</v>
+      </c>
+      <c r="E24">
+        <v>501</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>7.51359710550887</v>
+      </c>
+      <c r="E25">
+        <v>712</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>8.395521541950114</v>
+      </c>
+      <c r="E26">
+        <v>424</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>8.724489795918368</v>
+      </c>
+      <c r="E27">
+        <v>21</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>8.540027605244996</v>
+      </c>
+      <c r="E28">
+        <v>23</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>7.005031642286544</v>
+      </c>
+      <c r="E29">
+        <v>501</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>7.236010320915981</v>
+      </c>
+      <c r="E30">
+        <v>712</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>8.076536037062352</v>
+      </c>
+      <c r="E31">
+        <v>424</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>8.099773242630386</v>
+      </c>
+      <c r="E32">
+        <v>21</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>7.99447895100069</v>
+      </c>
+      <c r="E33">
+        <v>23</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Highest education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>8.178277189299234</v>
+      </c>
+      <c r="E34">
+        <v>502</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Drought</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>6.924712267495773</v>
+      </c>
+      <c r="E35">
+        <v>653</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Floods</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>7.966699735449735</v>
+      </c>
+      <c r="E36">
+        <v>487</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Public Health Emergency – Cholera and Diarrhea</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>8.666666666666666</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Strong Winds</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>8.281944444444445</v>
+      </c>
+      <c r="E38">
+        <v>40</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>7.750492063492064</v>
+      </c>
+      <c r="E39">
+        <v>502</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Drought</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>6.850682593856655</v>
+      </c>
+      <c r="E40">
+        <v>653</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Floods</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>7.652732590620789</v>
+      </c>
+      <c r="E41">
+        <v>487</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Public Health Emergency – Cholera and Diarrhea</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>7.936507936507936</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Main
+Hazard</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Strong Winds</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>7.96984126984127</v>
+      </c>
+      <c r="E43">
+        <v>40</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Which hazard is most affecting the district and your community in particular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Decreased</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>8.154320987654321</v>
+      </c>
+      <c r="E44">
+        <v>418</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>4.417906746031746</v>
+      </c>
+      <c r="E45">
+        <v>37</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Increased</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>7.577415254849286</v>
+      </c>
+      <c r="E46">
+        <v>1170</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Same/No change</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>7.493092298647854</v>
+      </c>
+      <c r="E47">
+        <v>55</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Decreased</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>7.909222569806511</v>
+      </c>
+      <c r="E48">
+        <v>418</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Don’t know</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>4.91344246031746</v>
+      </c>
+      <c r="E49">
+        <v>37</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Increased</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>7.283917340521114</v>
+      </c>
+      <c r="E50">
+        <v>1170</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Risk
+Change</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Same/No change</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>7.313949938949938</v>
+      </c>
+      <c r="E51">
+        <v>55</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>How your perception of risk, exposure, and need for action has changed in recent years?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Awareness
+of CLGRR</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>5.797642952763434</v>
+      </c>
+      <c r="E52">
+        <v>380</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Awareness of Community Local Groups for Risk Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Awareness
+of CLGRR</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>8.148746535651297</v>
+      </c>
+      <c r="E53">
+        <v>1294</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Awareness of Community Local Groups for Risk Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Awareness
+of CLGRR</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>5.735441767068273</v>
+      </c>
+      <c r="E54">
+        <v>380</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Awareness of Community Local Groups for Risk Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Awareness
+of CLGRR</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>7.830287565512151</v>
+      </c>
+      <c r="E55">
+        <v>1294</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Awareness of Community Local Groups for Risk Reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Interaction
+with CLGRR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>6.641332175694027</v>
+      </c>
+      <c r="E56">
+        <v>771</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Did you have any interaction with any member of CLGRD before or during the event?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Interaction
+with CLGRR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>8.494607129374966</v>
+      </c>
+      <c r="E57">
+        <v>905</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Did you have any interaction with any member of CLGRD before or during the event?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Interaction
+with CLGRR</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>6.350932154948775</v>
+      </c>
+      <c r="E58">
+        <v>771</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Did you have any interaction with any member of CLGRD before or during the event?</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Interaction
+with CLGRR</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>8.266259943130692</v>
+      </c>
+      <c r="E59">
+        <v>905</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Did you have any interaction with any member of CLGRD before or during the event?</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>6.229402872260015</v>
+      </c>
+      <c r="E60">
+        <v>177</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>6.812599206349206</v>
+      </c>
+      <c r="E61">
+        <v>198</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>dissemination</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>8.241081449414782</v>
+      </c>
+      <c r="E62">
+        <v>1209</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>5.991883116883117</v>
+      </c>
+      <c r="E63">
+        <v>177</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>6.646081349206349</v>
+      </c>
+      <c r="E64">
+        <v>198</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Received
+early
+warnings</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>7.930360313455351</v>
+      </c>
+      <c r="E65">
+        <v>1209</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Did you personally receive the warning(s) by Nepal Red Cross?</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2559,13 +4340,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Age Group</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2582,53 +4363,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>18-29</t>
         </is>
       </c>
       <c r="B2">
-        <v>1078</v>
+        <v>485</v>
       </c>
       <c r="C2">
-        <v>63.8</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B3">
-        <v>601</v>
+        <v>381</v>
       </c>
       <c r="C3">
-        <v>35.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other or did not answer</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>293</v>
       </c>
       <c r="C4">
-        <v>0.7</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B5">
-        <v>1690</v>
+        <v>222</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>309</v>
+      </c>
+      <c r="C6">
+        <v>18.3</v>
       </c>
     </row>
   </sheetData>
@@ -2638,31 +4432,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Total Respondents</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Locality</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Respondents</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
@@ -2671,139 +4455,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gaza</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>438</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1078</v>
+      </c>
+      <c r="C2">
+        <v>63.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gaza</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chigubo</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ndindiza-sede</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>249</v>
-      </c>
-      <c r="E3">
-        <v>56.8</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>601</v>
+      </c>
+      <c r="C3">
+        <v>35.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gaza</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chigubo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Saute</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>189</v>
-      </c>
-      <c r="E4">
-        <v>43.2</v>
+          <t>Other or did not answer</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sofala</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>1252</v>
-      </c>
-      <c r="E5">
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1690</v>
+      </c>
+      <c r="C5">
         <v>100</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sofala</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Buzi</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Vila Sede</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>676</v>
-      </c>
-      <c r="E6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sofala</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Buzi</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Estaquinha - Sede</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>576</v>
-      </c>
-      <c r="E7">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2813,6 +4511,181 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Locality</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total Respondents</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>438</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chigubo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ndindiza-sede</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>249</v>
+      </c>
+      <c r="E3">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chigubo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Saute</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>189</v>
+      </c>
+      <c r="E4">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sofala</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>1252</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sofala</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Buzi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Vila Sede</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>676</v>
+      </c>
+      <c r="E6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sofala</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Buzi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Estaquinha - Sede</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>576</v>
+      </c>
+      <c r="E7">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
